--- a/dataset/stats/Ground/China_Realistic.xlsx
+++ b/dataset/stats/Ground/China_Realistic.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,76 +425,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N95"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Rank_Info</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Сыграно игр</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Победы</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Процент побед</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Возрождения</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Наземные убийства</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Воздушные убийства</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Морские убийства</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Смерти</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Убийств за возрождение</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Убийств за смерть</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>SL за игру</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>RP за игру</t>
         </is>
@@ -491,70 +508,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>cn_al_khalid_1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Al-Khalid-I</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.7#1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>1,943,429</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>946,238</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>48.7%</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>2,418,748</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2,603,741</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>45,307</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>2,225,767</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>16,959</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>1,351</t>
         </is>
@@ -563,70 +585,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>cn_ztz_99a</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>ZTZ99A</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.3#2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>1,090,596</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>569,386</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>52.2%</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1,220,354</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>1,375,285</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>20,002</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>1,098,811</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>7,255</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>769</t>
         </is>
@@ -635,70 +662,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>cn_vt_5</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>VT5</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.7#3</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>813,719</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>400,194</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>49.2%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>893,436</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>710,598</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>10,421</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>797,128</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>4,890</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>547</t>
         </is>
@@ -707,70 +739,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>cn_m1a2t</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>M1A2T</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>663,270</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>360,077</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>54.3%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>789,585</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>1,071,124</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>7,177</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>723,028</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>8,888</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>834</t>
         </is>
@@ -779,70 +816,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>cn_ztz_96a_prot</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>ZTZ96A(P)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.3#5</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>610,405</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>286,669</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>47.0%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>739,025</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>764,115</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>5,560</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>666,210</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>14,974</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>1,168</t>
         </is>
@@ -851,70 +893,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>cn_vt_4b</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>VT4A1</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#6</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>582,585</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>295,304</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>50.7%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>628,917</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>660,204</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>9,851</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>533,469</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>6,834</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>643</t>
         </is>
@@ -923,70 +970,75 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>cn_pgz_09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>PGZ09</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#7</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>485,887</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>213,839</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>44.0%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>557,024</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>217,360</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>248,753</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>414,444</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>4,439</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>321</t>
         </is>
@@ -995,70 +1047,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>cn_zbd_04a</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>ZBD04A</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.0#8</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>429,252</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>198,861</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>46.3%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>470,914</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>341,948</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>14,526</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>403,216</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>4,615</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>482</t>
         </is>
@@ -1067,70 +1124,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>cn_wz_1001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>WZ1001(E)LCT</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.3#9</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>427,309</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>217,491</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>50.9%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>454,864</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>478,717</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>6,152</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>397,113</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>6,592</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>649</t>
         </is>
@@ -1139,70 +1201,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>cn_m18_hellcat</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>␗M18GMC</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.0#10</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>380,294</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>194,554</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>51.2%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>424,975</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>336,632</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>4,874</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>391,602</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>0.80</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>0.87</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>4,010</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>292</t>
         </is>
@@ -1211,70 +1278,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>cn_pgz_625_fb10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>CS/SA5</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.0#11</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>379,522</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>178,567</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>47.1%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>468,022</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>81,606</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>249,633</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>345,993</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>0.71</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>4,811</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>356</t>
         </is>
@@ -1283,70 +1355,75 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>cn_ztz_96</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>ZTZ96</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#12</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>378,455</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>194,768</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>51.5%</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>434,277</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>564,592</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>4,351</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>375,817</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>7,323</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>540</t>
         </is>
@@ -1355,70 +1432,75 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>cn_hj_9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>AFT09</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#13</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>356,965</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>167,198</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>46.8%</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>387,182</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>428,763</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>2,231</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>328,533</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>6,244</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>518</t>
         </is>
@@ -1427,70 +1509,75 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>cn_mbt2000</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>MBT-2000</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.7#14</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>333,966</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>159,653</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>47.8%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>384,403</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>350,566</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>4,918</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>334,838</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>0.92</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>6,311</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>605</t>
         </is>
@@ -1499,70 +1586,75 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>cn_wz_305</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>WZ305</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#15</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>333,197</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>158,326</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>47.5%</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>382,329</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>204,722</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>70,134</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>304,590</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>3,796</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>264</t>
         </is>
@@ -1571,70 +1663,75 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>cn_ztz_88b</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>ZTZ88B</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#16</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>306,136</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>160,215</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>52.3%</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>336,626</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>360,209</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>3,414</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>284,185</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>1.28</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>6,189</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>447</t>
         </is>
@@ -1643,70 +1740,75 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>cn_ztz_99</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>ZTZ99-II</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.0#17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>288,293</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>127,558</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>44.2%</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>319,793</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>298,969</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>2,277</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>280,837</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>5,903</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>527</t>
         </is>
@@ -1715,70 +1817,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>cn_t_34_85_d_5t</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>␗T-34-85(S-53)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.7#18</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>271,341</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>133,423</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>49.2%</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>295,301</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>260,904</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>251,113</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>3,185</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>244</t>
         </is>
@@ -1787,70 +1894,75 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>cn_t_80ud_478be</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>T-80UD/BE</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.0#19</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>252,688</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>113,045</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>44.7%</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>291,748</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>274,954</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>1,838</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>254,685</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>6,307</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>627</t>
         </is>
@@ -1859,70 +1971,75 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>cn_plz_05</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>PLZ05</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#20</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>251,408</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>121,283</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>48.2%</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>279,780</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>187,193</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>17,016</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>229,392</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>4,365</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>286</t>
         </is>
@@ -1931,70 +2048,75 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>cn_object_211</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Object211</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.0#21</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>241,713</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>121,163</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>50.1%</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>268,668</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>204,355</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>397</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>243,940</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>2,580</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>224</t>
         </is>
@@ -2003,70 +2125,75 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>cn_type_58</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>T-34-85Gai</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.7#22</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>237,399</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>120,755</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>50.9%</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>259,167</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>259,181</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>7,691</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>221,132</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>4,003</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>294</t>
         </is>
@@ -2075,70 +2202,75 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>cn_ztz_99_w</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>ZTZ99-III</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.0#23</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>232,822</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>106,060</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>45.6%</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>258,341</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>269,467</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>2,087</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>226,910</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>6,741</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>650</t>
         </is>
@@ -2147,70 +2279,75 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>cn_m24_chaffee</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>␗M24</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.7#24</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>229,923</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>120,663</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>52.5%</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>252,944</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>221,981</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>6,669</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>222,673</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>1,918</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>226</t>
         </is>
@@ -2219,70 +2356,75 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>cn_ztz_96a</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>ZTZ96A</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.3#25</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>222,160</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>98,539</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>44.4%</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>251,284</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>232,096</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>1,813</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>219,247</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>5,750</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>487</t>
         </is>
@@ -2291,70 +2433,75 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>cn_type_59d</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>ZTZ59D1</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.3#26</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>220,600</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>118,163</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>53.6%</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>253,198</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>276,513</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>3,612</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>210,586</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>6,328</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>447</t>
         </is>
@@ -2363,70 +2510,75 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>cn_hq_11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>HQ11</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#27</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>219,810</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>111,629</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>50.8%</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>248,786</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>252,530</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>169,792</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>5,052</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>362</t>
         </is>
@@ -2435,70 +2587,75 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>cn_type_69</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>Type69</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#28</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>212,680</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>115,288</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>54.2%</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>239,297</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>251,454</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>4,348</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>200,285</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>1.28</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>6,611</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>451</t>
         </is>
@@ -2507,70 +2664,75 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>cn_ztz_88a</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>ZTZ88A</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#29</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>208,382</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>114,206</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>54.8%</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>226,057</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>279,909</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>3,763</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>188,692</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>7,262</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>545</t>
         </is>
@@ -2579,70 +2741,75 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>cn_ptz_89</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>PTZ89</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#30</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>196,423</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>96,088</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>48.9%</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>213,853</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>239,695</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>2,822</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>179,633</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>6,189</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>434</t>
         </is>
@@ -2651,70 +2818,75 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>cn_pgz_04a</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>PGZ04A</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#31</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>195,103</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>80,922</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>41.5%</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>228,290</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>47,342</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>100,381</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>163,454</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>3,864</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>267</t>
         </is>
@@ -2723,70 +2895,75 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>cn_t_34_1942</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>␗T-34(1943)</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.0#32</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>194,748</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>100,779</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>51.7%</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>214,138</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>217,671</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>703</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>183,780</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>2,731</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>254</t>
         </is>
@@ -2795,70 +2972,75 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>cn_object_122tm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Object122MT""MC</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#33</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>194,566</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>104,624</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>53.8%</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>232,015</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>271,549</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>3,241</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>200,743</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>1.18</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>7,115</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>505</t>
         </is>
@@ -2867,70 +3049,75 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>cn_vt_4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>VT4</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.3#34</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>192,979</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>100,004</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>51.8%</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>216,738</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>192,041</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>2,208</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>194,553</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>6,182</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>535</t>
         </is>
@@ -2939,70 +3126,75 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>cn_type_59</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>Type59</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#35</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>191,267</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>99,988</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>52.3%</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>209,029</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>176,192</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>2,996</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>172,834</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>5,243</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>349</t>
         </is>
@@ -3011,70 +3203,75 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>cn_zsl_92</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>ZSL92</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.3#36</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>184,661</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>83,764</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>45.4%</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>209,360</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>62,195</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>38,939</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>167,662</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>0.60</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>3,297</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>231</t>
         </is>
@@ -3083,70 +3280,75 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>cn_m36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>␗M36GMC</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.3#37</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>177,707</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>86,525</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>48.7%</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>197,747</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>163,399</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>3,566</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>174,311</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>3,173</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>226</t>
         </is>
@@ -3155,70 +3357,75 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>cn_m8_greyhound</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>␗M8LAC</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#38</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>175,942</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>87,807</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>49.9%</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>211,276</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>204,963</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>13,970</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>187,998</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>347</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>218</t>
         </is>
@@ -3227,70 +3434,75 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>cn_ptl_02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>PTL02</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#39</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>170,511</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>92,742</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>54.4%</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>184,956</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>149,103</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>1,918</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>159,769</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>4,273</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>364</t>
         </is>
@@ -3299,70 +3511,75 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>cn_is_2_1943</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>␗IS-2</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.3#40</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>169,341</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>78,412</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>46.3%</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>184,483</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>150,886</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>287</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>154,747</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>4,239</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>259</t>
         </is>
@@ -3371,70 +3588,75 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>cn_m42_duster</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>␗M42</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.0#41</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>167,732</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>76,515</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>45.6%</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>193,765</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>76,207</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>32,287</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>156,630</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>0.56</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>1,773</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>159</t>
         </is>
@@ -3443,70 +3665,75 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>cn_zsd63_pg87</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>ZSD63/PG87</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Ранг 4БР 5.7#42</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>164,281</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>73,310</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>44.6%</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>185,490</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>53,911</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>67,005</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>129,863</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>2,935</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>203</t>
         </is>
@@ -3515,70 +3742,75 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>cn_cm11</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>CM11</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#43</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>163,589</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>84,157</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>51.4%</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>179,920</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>204,028</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>1,960</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>153,397</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>6,557</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>486</t>
         </is>
@@ -3587,70 +3819,75 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>cn_m60a3_tts</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>␗M60A3TTS</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#44</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>162,126</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>85,472</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>52.7%</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>178,692</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>194,880</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>1,686</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>151,155</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>6,368</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>461</t>
         </is>
@@ -3659,70 +3896,75 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>cn_m4a4_sherman</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>␗M4A4</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.7#45</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>147,460</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>74,088</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>50.2%</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>162,672</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>157,314</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>1,451</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>136,773</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>2,185</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>222</t>
         </is>
@@ -3731,70 +3973,75 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>cn_cm_34</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>CM34</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#46</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>139,723</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>74,214</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>53.1%</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>161,526</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>127,379</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>6,729</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>143,809</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>5,020</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>425</t>
         </is>
@@ -3803,70 +4050,75 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>cn_type_69_2g</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>T-69IIG</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#47</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>137,958</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>76,861</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>55.7%</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>162,179</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>222,774</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>3,791</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>137,360</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>20,383</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>1,405</t>
         </is>
@@ -3875,70 +4127,75 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>cn_sdkfz_222_early</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>␗Sd.Kfz.222</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.3#48</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>132,279</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>63,919</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>48.3%</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>157,041</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>86,964</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>19,769</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>135,689</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>346</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>154</t>
         </is>
@@ -3947,70 +4204,75 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>cn_m48a1_patton_III</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>␗M48A1</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#49</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>130,293</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>64,599</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>49.6%</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>145,075</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>89,453</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>1,017</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>123,980</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>0.62</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>4,465</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>294</t>
         </is>
@@ -4019,70 +4281,75 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>cn_wma_301</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>WMA301</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.0#50</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>125,726</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>68,462</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>54.5%</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>141,800</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>139,865</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>2,780</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>123,691</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>11,824</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>999</t>
         </is>
@@ -4091,70 +4358,75 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>cn_su_100_1945</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>␗SU-100</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.0#51</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>125,387</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>59,486</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>47.4%</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>137,037</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>127,340</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>115,557</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>4,785</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>280</t>
         </is>
@@ -4163,70 +4435,75 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>cn_type_62</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>Type62</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#52</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>125,119</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>61,687</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>49.3%</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>141,449</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>93,612</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>2,423</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>126,513</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>3,968</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>293</t>
         </is>
@@ -4235,70 +4512,75 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>cn_zts_63_1980</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>ZTS63</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#53</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>124,444</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>63,338</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>50.9%</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>137,907</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>73,031</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>1,818</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>123,415</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>0.61</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>3,379</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>259</t>
         </is>
@@ -4307,70 +4589,75 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>cn_type_63_I</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>Type63</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.3#54</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>121,978</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>58,828</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>48.2%</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>132,460</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>78,788</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>119,769</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>0.60</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>3,204</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>236</t>
         </is>
@@ -4379,70 +4666,75 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>cn_m10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>␗M10GMC</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.3#55</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>117,631</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>56,318</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>47.9%</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>129,749</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>100,801</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>2,949</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>111,859</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>0.80</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>1,698</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>177</t>
         </is>
@@ -4451,70 +4743,75 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>cn_m_41d</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>M41D</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.0#56</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>101,115</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>54,005</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>53.4%</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>109,582</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>57,294</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>1,532</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>88,685</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>3,654</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>304</t>
         </is>
@@ -4523,70 +4820,75 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>cn_type_65_aa</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>PhòngkhôngT-34</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.0#57</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>98,588</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>44,053</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>44.7%</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>111,888</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>26,027</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>15,864</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>89,318</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>0.37</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>2,068</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>155</t>
         </is>
@@ -4595,70 +4897,75 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>cn_m55</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>␗M55</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.0#58</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>98,466</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>47,524</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>48.3%</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>108,130</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>78,963</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>2,569</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>91,437</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>2,270</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>198</t>
         </is>
@@ -4667,70 +4974,75 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>cn_lvt_4_zis_2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>LVT(A)(4)(ZiS-2)</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.3#59</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>96,195</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>46,617</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>48.5%</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>106,936</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>88,908</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>422</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>95,034</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>1,122</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>169</t>
         </is>
@@ -4739,70 +5051,75 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>cn_plz_83</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>PLZ83</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.3#60</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>93,606</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>43,285</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>46.2%</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>102,788</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>55,937</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>4,812</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>87,987</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>3,663</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>225</t>
         </is>
@@ -4811,70 +5128,75 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>cn_ztl_11</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>ZLT11</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Ранг 7БР 9.7#61</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>91,949</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>44,724</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>48.6%</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>102,818</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>70,065</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>1,000</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>90,854</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>0.78</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>4,240</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>402</t>
         </is>
@@ -4883,70 +5205,75 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>cn_oplot_t</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>Oplot-M</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.3#62</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>91,886</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>48,489</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>52.8%</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>115,055</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>118,602</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>757</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>104,201</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>7,835</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>859</t>
         </is>
@@ -4955,70 +5282,75 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>cn_m4a1_76w_sherman</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>␗M4A1(75)W</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.0#63</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>89,360</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>46,533</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>52.1%</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>96,225</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>100,759</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>3,449</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>80,631</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>1.29</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>3,126</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>265</t>
         </is>
@@ -5027,70 +5359,75 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>cn_gmc_cckw_353_m45_quad</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>CCKW353(M45)</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.3#64</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>88,675</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>38,451</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>43.4%</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>101,930</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>11,501</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>36,351</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>76,898</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>0.62</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>119</t>
         </is>
@@ -5099,70 +5436,75 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>cn_m8_scott</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>␗M8HMC</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.3#65</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>86,532</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>41,874</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>48.4%</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>96,092</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>66,901</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>6,047</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>83,787</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>0.87</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>150</t>
         </is>
@@ -5171,70 +5513,75 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>cn_su_76m_1943</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>␗SU-76M</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Ранг 1БР 2.0#66</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>86,450</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>39,945</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>46.2%</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>95,027</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>76,107</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>83,348</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>0.80</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>0.92</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>749</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>141</t>
         </is>
@@ -5243,70 +5590,75 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>cn_is_2_1944</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>␗IS-2(1944)</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#67</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>83,054</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>39,742</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>47.9%</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>91,320</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>89,260</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>2,327</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>74,553</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>5,479</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>335</t>
         </is>
@@ -5315,70 +5667,75 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>cn_m113a1_tow</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>␗M113A1(TOW)</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.3#68</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>82,999</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>40,867</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>49.2%</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>89,542</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>55,242</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>1,102</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>75,907</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>4,013</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>262</t>
         </is>
@@ -5387,70 +5744,75 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>cn_isu_152</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>␗ISU-152</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.7#69</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>79,557</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>37,235</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>46.8%</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>85,793</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>61,514</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>3,497</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>69,186</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>2,621</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>204</t>
         </is>
@@ -5459,70 +5821,75 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>cn_t_26_1940</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>␗T-26</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#70</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>72,980</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>33,678</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>46.1%</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>83,820</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>62,695</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>3,569</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>69,672</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>141</t>
         </is>
@@ -5531,70 +5898,75 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>cn_wz_141</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>WZ141-1</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#71</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>70,422</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>36,693</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>52.1%</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>88,317</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>102,703</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>730</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t>81,943</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>14,586</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>1,062</t>
         </is>
@@ -5603,70 +5975,75 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>cn_m3a3_stuart</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>␗M3A3Stuart</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#72</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>69,044</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>35,097</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>50.8%</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>75,511</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>51,804</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>1,404</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>66,558</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>0.80</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>1,221</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>205</t>
         </is>
@@ -5675,70 +6052,75 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>cn_type_86</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>ZBD86</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#73</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>65,968</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>34,609</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>52.5%</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>70,870</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>31,716</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>61,728</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>3,133</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>248</t>
         </is>
@@ -5747,70 +6129,75 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>cn_type_97_kai</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>␗Chi-HaKai</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.3#74</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>64,468</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>31,291</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>48.5%</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>70,374</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>60,169</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>935</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>59,268</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>0.87</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>1,025</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>179</t>
         </is>
@@ -5819,70 +6206,75 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>cn_tor_m1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>Tor-M1</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Ранг 8БР 11.3#75</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>64,019</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>28,453</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>44.4%</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>77,953</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>49,314</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>53,856</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>0.64</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>3,344</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>236</t>
         </is>
@@ -5891,70 +6283,75 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>cn_hq_17</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>HQ17</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Ранг 8БР 11.7#76</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>52,917</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>24,452</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>46.2%</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>73,822</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>650</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>42,503</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>50,472</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>0.58</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>3,576</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>261</t>
         </is>
@@ -5963,70 +6360,75 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>cn_type_97_chi_ha</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>␗Chi-Ha</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.3#77</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>52,494</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>23,757</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>45.3%</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>56,229</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>29,563</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>1,384</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t>46,903</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>0.55</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>295</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>115</t>
         </is>
@@ -6035,70 +6437,75 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>cn_qn506</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>QN506</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.0#78</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>51,591</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>24,835</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>48.1%</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>57,979</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>40,889</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>4,623</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t>48,474</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>0.78</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>5,319</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>580</t>
         </is>
@@ -6107,70 +6514,75 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>cn_m41_a3_walker_bulldog</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>␗M41A3</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.7#79</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>44,099</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>23,637</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>53.6%</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>52,734</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>52,509</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>1,424</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t>47,703</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>10,909</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>820</t>
         </is>
@@ -6179,70 +6591,75 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>cn_cm_25</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>CM25</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#80</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>39,830</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>19,450</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>48.8%</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>43,133</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>26,480</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>471</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t>36,580</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>0.62</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>4,284</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>307</t>
         </is>
@@ -6251,70 +6668,75 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>cn_antelope_tc_1l_ads</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>Antelope</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.0#81</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>32,331</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>13,773</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>42.6%</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>43,233</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>14,910</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t>26,444</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>0.56</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>2,938</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>217</t>
         </is>
@@ -6323,70 +6745,75 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>cn_ztz_59a</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>ZTZ59A</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#82</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>28,158</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>15,842</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>56.3%</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>34,689</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>43,416</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>750</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>29,310</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>18,821</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>1,218</t>
         </is>
@@ -6395,70 +6822,75 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>cn_type_69_2a</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>Type69-IIa</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.3#83</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>26,559</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>15,126</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>57.0%</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>32,263</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>40,169</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>603</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t>27,006</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>18,856</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>1,243</t>
         </is>
@@ -6467,70 +6899,75 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>cn_m5a1_stuart</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>␗M5A1</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#84</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>25,620</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>13,545</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>52.9%</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>28,117</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>25,109</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>786</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>24,054</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>0.92</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>1,915</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>266</t>
         </is>
@@ -6539,70 +6976,75 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>cn_plz_83_130</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>PLZ83-130</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.3#85</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>24,210</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>12,413</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>51.3%</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>29,459</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>36,814</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>1,691</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>25,305</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>7,900</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>520</t>
         </is>
@@ -6611,70 +7053,75 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>cn_t_62</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>T-62N545</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#86</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>23,327</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>12,770</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>54.7%</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>26,213</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>29,392</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>212</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t>21,764</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>16,336</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>1,135</t>
         </is>
@@ -6683,70 +7130,75 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>cn_type_64</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>M64</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.0#87</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>22,823</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>12,627</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>55.3%</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>26,597</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>33,497</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>704</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>23,840</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>1.29</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>11,391</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>812</t>
         </is>
@@ -6755,70 +7207,75 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>cn_m4a4_sherman_1st_ptg</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>␗M4A4(1stPTG)</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.7#88</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>22,128</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>12,538</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>56.7%</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>26,875</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>43,611</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>1,013</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t>23,390</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>1.66</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>1.91</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>9,402</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>848</t>
         </is>
@@ -6827,70 +7284,75 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>cn_isu_122</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>␗ISU-122</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.3#89</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>21,767</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>10,392</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>47.7%</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>23,418</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>19,834</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>1,188</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t>18,629</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>3,845</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>260</t>
         </is>
@@ -6899,70 +7361,75 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>cn_t_34_85_zis_53_no215</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>T-34-85No.215</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Ранг 4БР 5.7#90</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>19,465</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>10,648</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>54.7%</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>22,722</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>35,287</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t>19,556</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>1.56</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>16,491</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>1,062</t>
         </is>
@@ -6971,70 +7438,75 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>cn_t_26_no531</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>T-26No.531</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#91</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>10,511</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>4,698</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>44.7%</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>11,591</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>8,080</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>346</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t>9,927</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>735</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>184</t>
         </is>
@@ -7043,70 +7515,75 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>cn_m3a3_stuart_1st_ptg</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>␗M3A3(1stPTG)</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#92</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>9,084</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>4,885</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>53.8%</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>11,166</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>11,161</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t>10,009</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>3,554</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>662</t>
         </is>
@@ -7115,70 +7592,75 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>cn_pt_76</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>␗PT-76</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.0#93</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>8,812</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>4,436</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>50.3%</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>9,513</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>5,686</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t>8,268</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>0.61</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>2,661</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>218</t>
         </is>
@@ -7187,70 +7669,75 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>cn_is_2_1943_no402</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>IS-2No.402</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.3#94</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>6,715</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>3,230</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>48.1%</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>8,107</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>8,162</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t>7,043</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>13,709</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>840</t>
         </is>
